--- a/fixtures/xlsx/path-many-columns/input.xlsx
+++ b/fixtures/xlsx/path-many-columns/input.xlsx
@@ -10,34 +10,34 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
+    <t>Col6</t>
+  </si>
+  <si>
+    <t>Col7</t>
+  </si>
+  <si>
+    <t>Col2</t>
+  </si>
+  <si>
     <t>Col3</t>
   </si>
   <si>
-    <t>Col10</t>
+    <t>Col4</t>
   </si>
   <si>
     <t>Col5</t>
   </si>
   <si>
-    <t>Col6</t>
+    <t>Col9</t>
   </si>
   <si>
-    <t>Col4</t>
-  </si>
-  <si>
-    <t>Col2</t>
+    <t>Col1</t>
   </si>
   <si>
     <t>Col8</t>
   </si>
   <si>
-    <t>Col1</t>
-  </si>
-  <si>
-    <t>Col9</t>
-  </si>
-  <si>
-    <t>Col7</t>
+    <t>Col10</t>
   </si>
 </sst>
 </file>
@@ -50,31 +50,31 @@
         <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
       <c r="J1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2">

--- a/fixtures/xlsx/path-many-columns/input.xlsx
+++ b/fixtures/xlsx/path-many-columns/input.xlsx
@@ -10,6 +10,15 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
+    <t>Col10</t>
+  </si>
+  <si>
+    <t>Col4</t>
+  </si>
+  <si>
+    <t>Col3</t>
+  </si>
+  <si>
     <t>Col6</t>
   </si>
   <si>
@@ -19,10 +28,7 @@
     <t>Col2</t>
   </si>
   <si>
-    <t>Col3</t>
-  </si>
-  <si>
-    <t>Col4</t>
+    <t>Col8</t>
   </si>
   <si>
     <t>Col5</t>
@@ -33,12 +39,6 @@
   <si>
     <t>Col1</t>
   </si>
-  <si>
-    <t>Col8</t>
-  </si>
-  <si>
-    <t>Col10</t>
-  </si>
 </sst>
 </file>
 
@@ -47,34 +47,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
-        <v>5</v>
+      <c r="H1" t="s">
+        <v>6</v>
       </c>
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">
